--- a/data/reports/monthly_factsheet.xlsx
+++ b/data/reports/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-06 07:50</t>
+          <t>Generated: 2026-06-10 09:19</t>
         </is>
       </c>
     </row>
@@ -461,21 +461,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Portfolio Holdings: 0</t>
+          <t>Portfolio Holdings: 36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Risk Records: 0</t>
+          <t>Risk Records: 10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rebalance Actions: 0</t>
+          <t>Rebalance Actions: 36</t>
         </is>
       </c>
     </row>
@@ -490,10 +490,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,6 +502,78 @@
         <is>
           <t>Performance Metrics</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total Return</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>585.91</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>34.89</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Max Drawdown</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-28.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>59.6</v>
       </c>
     </row>
   </sheetData>
@@ -514,10 +587,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,6 +601,349 @@
         <is>
           <t>Top Holdings</t>
         </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FINAL_WEIGHT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EXPECTED_RETURN_30D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CONVICTION_SCORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0316663489686118</v>
+      </c>
+      <c r="C4" t="n">
+        <v>124.55467</v>
+      </c>
+      <c r="D4" t="n">
+        <v>52.25184</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CONFIPET</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0395096397302414</v>
+      </c>
+      <c r="C5" t="n">
+        <v>103.12096</v>
+      </c>
+      <c r="D5" t="n">
+        <v>47.54430758766732</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CPPLUS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0433257368359144</v>
+      </c>
+      <c r="C6" t="n">
+        <v>82.88988000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>45.21248349116256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IDEAFORGE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0329134749965033</v>
+      </c>
+      <c r="C7" t="n">
+        <v>94.50532</v>
+      </c>
+      <c r="D7" t="n">
+        <v>42.6485518546659</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IBULLSLTD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0343593666507723</v>
+      </c>
+      <c r="C8" t="n">
+        <v>85.89438000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>43.49980178182961</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0325651061035051</v>
+      </c>
+      <c r="C9" t="n">
+        <v>81.16306</v>
+      </c>
+      <c r="D9" t="n">
+        <v>39.19456389832192</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BLISSGVS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0194630528749825</v>
+      </c>
+      <c r="C10" t="n">
+        <v>81.53052</v>
+      </c>
+      <c r="D10" t="n">
+        <v>38.9896264268919</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IOLCP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0371882733022332</v>
+      </c>
+      <c r="C11" t="n">
+        <v>63.98594000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39.85443765669003</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0256380338005201</v>
+      </c>
+      <c r="C12" t="n">
+        <v>63.82895000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>36.71006859513176</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0294898582135803</v>
+      </c>
+      <c r="C13" t="n">
+        <v>61.34618999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>36.18375863096582</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0340033629881677</v>
+      </c>
+      <c r="C14" t="n">
+        <v>51.69411</v>
+      </c>
+      <c r="D14" t="n">
+        <v>37.67397472316694</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0413772095426265</v>
+      </c>
+      <c r="C15" t="n">
+        <v>43.02279000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>36.55699193527308</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>APCOTEXIND</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0401992938730168</v>
+      </c>
+      <c r="C16" t="n">
+        <v>44.55772</v>
+      </c>
+      <c r="D16" t="n">
+        <v>33.83310043681863</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.039911293914623</v>
+      </c>
+      <c r="C17" t="n">
+        <v>42.89037</v>
+      </c>
+      <c r="D17" t="n">
+        <v>34.41599246313125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EFFWA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0280010614580337</v>
+      </c>
+      <c r="C18" t="n">
+        <v>52.79942</v>
+      </c>
+      <c r="D18" t="n">
+        <v>33.75172583744793</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.0350039941826131</v>
+      </c>
+      <c r="C19" t="n">
+        <v>40.07446</v>
+      </c>
+      <c r="D19" t="n">
+        <v>36.82498128960079</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0333680407371307</v>
+      </c>
+      <c r="C20" t="n">
+        <v>38.47247999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>36.04329204038034</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0229080147699214</v>
+      </c>
+      <c r="C21" t="n">
+        <v>53.55762000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31.48923893046965</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AIMTRON</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0171830677133966</v>
+      </c>
+      <c r="C22" t="n">
+        <v>47.87674000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>34.15943750091908</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0357180473874277</v>
+      </c>
+      <c r="C23" t="n">
+        <v>30.70578</v>
+      </c>
+      <c r="D23" t="n">
+        <v>33.45263867771638</v>
       </c>
     </row>
   </sheetData>
@@ -538,10 +957,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,6 +969,118 @@
         <is>
           <t>Portfolio Risk</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Portfolio Volatility</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>23.04</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VaR95</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CVaR95</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Current Drawdown</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Max Drawdown</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-16.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Largest Position</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Top5 Exposure</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20.43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Top10 Exposure</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>38.06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Health Score</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>88.69</v>
       </c>
     </row>
   </sheetData>
@@ -562,10 +1094,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AS38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="42" max="42"/>
+    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="25" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,6 +1149,5453 @@
         <is>
           <t>Factor Attribution</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ALPHA_RANK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MarketCap</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ALPHA_SCORE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RS_30D</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>RS_60D</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>RS_ACCELERATION</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>VOL_ADJ_RS</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>SECTOR_SCORE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ENTRY_SCORE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LIQUIDITY_SCORE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>FACTOR_MOMENTUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>FACTOR_SHARPE</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>FACTOR_ALPHA</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>RS_COMPOSITE</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>FACTOR_RS</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>FACTOR_LOW_VOL</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>FACTOR_SECTOR</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>FACTOR_ENTRY</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>FACTOR_LIQUIDITY</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>MULTI_FACTOR_SCORE</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>FACTOR_RANK</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>INITIAL_WEIGHT</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>INITIAL_WEIGHT_%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>POSITION_SCORE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TARGET_WEIGHT</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>TARGET_WEIGHT_%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>YF_SYMBOL</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>VOLATILITY</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>EXPECTED_RETURN_30D</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>RETURN_NORM</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>CONVICTION_SCORE</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>RISK_SCORE</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>FINAL_WEIGHT</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>FINAL_WEIGHT_%</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION_%</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>ALPHA_CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>RISK_ADJ_CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>ATTRIBUTION_RANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CONFIPET</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas Refining &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>25785229312</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.4256</v>
+      </c>
+      <c r="G3" t="n">
+        <v>128.916</v>
+      </c>
+      <c r="H3" t="n">
+        <v>232.22</v>
+      </c>
+      <c r="I3" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J3" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-34.03</v>
+      </c>
+      <c r="L3" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>72.23168654173764</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="R3" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="T3" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="U3" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="V3" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="W3" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="X3" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.0300252075486388</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>15417.9045</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.0341135066839544</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>CONFIPET.NS</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.524867637266319</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>103.12096</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.8279172511155144</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>47.54430758766732</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>815.250813552997</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0395096397302414</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4.074271978236634</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.994800051914365</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7.762475125074895</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Communication Equipment</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>286511267840</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.4367</v>
+      </c>
+      <c r="G4" t="n">
+        <v>147.74</v>
+      </c>
+      <c r="H4" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="I4" t="n">
+        <v>94.61</v>
+      </c>
+      <c r="J4" t="n">
+        <v>183.16</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-89.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>175.92</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>99.48892674616695</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>100</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="n">
+        <v>62.67333333333332</v>
+      </c>
+      <c r="U4" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="V4" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="W4" t="n">
+        <v>94.87</v>
+      </c>
+      <c r="X4" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.0295742616978273</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12465.2184</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0275804219182542</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>HFCL.NS</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.4798071041527482</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>124.55467</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>52.25184</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>653.4105837253145</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.0316663489686118</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3.944191645890283</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2.277527911699102</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.220369418779253</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CPPLUS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Building Products &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>412700606464</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.9808</v>
+      </c>
+      <c r="G5" t="n">
+        <v>97.33199999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>266.91</v>
+      </c>
+      <c r="I5" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>117.36</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-45.75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>153.04</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>88.75638841567292</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="R5" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="S5" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="T5" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="V5" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="W5" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="X5" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.0293536550945526</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14735.93472</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.0326045869310603</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>CPPLUS.NS</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.4551627827133646</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>82.88988000000001</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.6654899410837025</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>45.21248349116256</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>893.9930215619432</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.0433257368359144</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3.591265127240524</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.310944323187469</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7.890067605773685</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IDEAFORGE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Computer Hardware</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>41002508288</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.0412</v>
+      </c>
+      <c r="G6" t="n">
+        <v>110.138</v>
+      </c>
+      <c r="H6" t="n">
+        <v>188.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>129.83</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-67.90000000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>82.62350936967631</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="T6" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="U6" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>94.87</v>
+      </c>
+      <c r="X6" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.0299635674683121</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15354.66528</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0339735841961638</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>IDEAFORGE.NS</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.5651775336157424</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>94.50532</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.7587456977727132</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>42.6485518546659</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>679.1440633465792</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0329134749965033</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3.110498486856544</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.378195997635126</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.503577728854549</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IBULLSLTD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Real Estate - Development</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>51903754240</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.7118</v>
+      </c>
+      <c r="G7" t="n">
+        <v>107.468</v>
+      </c>
+      <c r="H7" t="n">
+        <v>204.86</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="J7" t="n">
+        <v>151.86</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-29.51</v>
+      </c>
+      <c r="L7" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>62.86201022146509</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="R7" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="S7" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="T7" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="U7" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="V7" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="W7" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="X7" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.0295126216175006</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14895.97362</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.0329586874565138</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.5522000813492712</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>85.89438000000001</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6896118788641167</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>43.49980178182961</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>708.9789177137779</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0343593666507723</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.951276495660764</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.142873816103906</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.344578161686391</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Construction</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>191165235200</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.3866</v>
+      </c>
+      <c r="G8" t="n">
+        <v>94.006</v>
+      </c>
+      <c r="H8" t="n">
+        <v>177</v>
+      </c>
+      <c r="I8" t="n">
+        <v>71.92</v>
+      </c>
+      <c r="J8" t="n">
+        <v>108.73</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-67.23</v>
+      </c>
+      <c r="L8" t="n">
+        <v>117.08</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>84.83816013628621</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>37.80666666666666</v>
+      </c>
+      <c r="U8" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="V8" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="X8" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.0291882001420966</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14570.28162</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.0322380644808747</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>CEMPRO.NS</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.5249617698383903</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>81.16306</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6516259888127841</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>39.19456389832192</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>671.9557410694722</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0325651061035051</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.64308366058515</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.9291165279486038</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.034811699523996</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IOLCP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38651703296</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.1294</v>
+      </c>
+      <c r="G9" t="n">
+        <v>76.52000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>193.57</v>
+      </c>
+      <c r="I9" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-43.07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>81.60136286201022</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="R9" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="S9" t="n">
+        <v>98.39</v>
+      </c>
+      <c r="T9" t="n">
+        <v>33.26000000000001</v>
+      </c>
+      <c r="U9" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="V9" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="W9" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="X9" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>87.56</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0296067038453677</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>14991.09768</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0331691580335378</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>IOLCP.NS</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.4674390705899278</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>63.98594000000001</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.5137177112668679</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>39.85443765669003</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>767.3512153306493</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0371882733022332</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.379526624220296</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.4222328891118332</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.090559976548886</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Electronic Components</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>107387936768</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.0019</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70.78999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>142.92</v>
+      </c>
+      <c r="I10" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-48.83</v>
+      </c>
+      <c r="L10" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="R10" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="T10" t="n">
+        <v>29.20666666666666</v>
+      </c>
+      <c r="U10" t="n">
+        <v>97.29000000000001</v>
+      </c>
+      <c r="V10" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>94.87</v>
+      </c>
+      <c r="X10" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.0284031001716189</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13797.0045</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.0305271189887898</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>AVALON.NS</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.5351744006793155</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>61.34618999999999</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.4925242064388272</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>36.18375863096582</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>608.5003828010618</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.0294898582135803</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.809090445043357</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.2569798035629588</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.380375523842351</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>APCOTEXIND</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Specialty Chemicals</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>28006647808</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.3972</v>
+      </c>
+      <c r="G11" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>125.17</v>
+      </c>
+      <c r="I11" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-27.63</v>
+      </c>
+      <c r="L11" t="n">
+        <v>88.87</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>44.97444633730835</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>95.39</v>
+      </c>
+      <c r="R11" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="S11" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>23.81666666666666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="V11" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="W11" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="X11" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.0283998559568649</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13793.85288</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.0305201457447971</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>APCOTEXIND.NS</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.3670943596220834</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>44.55772</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3577362454575167</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>33.83310043681863</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>829.4812926159979</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.0401992938730168</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.791188880591598</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.32458093248856</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.879369114893492</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Specialty Chemicals</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>345636208640</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.5659</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50.088</v>
+      </c>
+      <c r="H12" t="n">
+        <v>166.78</v>
+      </c>
+      <c r="I12" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="J12" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-22.97</v>
+      </c>
+      <c r="L12" t="n">
+        <v>104.16</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>98.46678023850085</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="R12" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="S12" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="T12" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="U12" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="W12" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="X12" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.0291070947732456</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14489.42112</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.0320591533190356</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>HSCL.NS</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.385357301699822</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>43.02279000000001</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.345412901820542</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>36.55699193527308</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>853.7866701011563</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.0413772095426265</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.780162996938416</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.3976028905998349</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.619512823776963</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Utilities - Renewable</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2513096671232</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.8811</v>
+      </c>
+      <c r="G13" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="H13" t="n">
+        <v>170.25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="J13" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-28.55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="M13" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="R13" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="T13" t="n">
+        <v>29.00666666666666</v>
+      </c>
+      <c r="U13" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="V13" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="W13" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.0286204625601396</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14008.98312</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.0309961408373962</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN.NS</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.4832522765294169</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>51.69411</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.4150314877796232</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>37.67397472316694</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>701.6330578793717</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.0340033629881677</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.75777358668027</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.0318919029880263</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.637382940653916</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Thermal Coal</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4182092546048</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.4517</v>
+      </c>
+      <c r="G14" t="n">
+        <v>49.048</v>
+      </c>
+      <c r="H14" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="J14" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-36.08</v>
+      </c>
+      <c r="L14" t="n">
+        <v>98.26000000000001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>98.97785349233391</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="T14" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="U14" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="W14" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="X14" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.0290551873371809</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14437.78848</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.031944911438127</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>ADANIENT.NS</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.3761134188766699</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>42.89037</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.3443497542083328</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34.41599246313125</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>823.5386365455585</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.039911293914623</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.711810163176929</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.388801631952398</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.551313718849906</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55545839616</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.8235</v>
+      </c>
+      <c r="G15" t="n">
+        <v>76.834</v>
+      </c>
+      <c r="H15" t="n">
+        <v>145.62</v>
+      </c>
+      <c r="I15" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="J15" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-38.43</v>
+      </c>
+      <c r="L15" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>84.32708688245314</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>98.16</v>
+      </c>
+      <c r="R15" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="S15" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>34.74333333333333</v>
+      </c>
+      <c r="U15" t="n">
+        <v>98.16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="W15" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="X15" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.028899465028987</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13489.91888</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.0298476643099509</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>AEROFLEX.NS</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.5551397122338578</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>63.82895000000001</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.5124573008784016</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>36.71006859513176</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>529.0209694768483</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.0256380338005201</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.636448777551708</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.287067413958159</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.947814291589246</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BLISSGVS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>46372597760</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.4372</v>
+      </c>
+      <c r="G16" t="n">
+        <v>95.58199999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="J16" t="n">
+        <v>114.53</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-63.29</v>
+      </c>
+      <c r="L16" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>89.26746166950596</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="R16" t="n">
+        <v>98.16</v>
+      </c>
+      <c r="S16" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="T16" t="n">
+        <v>39.46666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="V16" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="W16" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.029139536920786</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12101.4486</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.0267755483698599</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>BLISSGVS.NS</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.5825070563690763</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>81.53052</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.6545761792793479</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>38.9896264268919</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>401.6050209237784</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.0194630528749825</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.586832821684818</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.5624531429434459</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.724143517807279</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EFFWA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5069229568</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5282</v>
+      </c>
+      <c r="G17" t="n">
+        <v>61.23400000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="J17" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-24.89</v>
+      </c>
+      <c r="L17" t="n">
+        <v>85.45999999999999</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="S17" t="n">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="T17" t="n">
+        <v>30.88333333333334</v>
+      </c>
+      <c r="U17" t="n">
+        <v>97.58</v>
+      </c>
+      <c r="V17" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="X17" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>83.34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.0270372857601681</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12502.00008</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.0276618047084075</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>EFFWA.NS</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.5257458194357753</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>52.79942</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.4239055829861699</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>33.75172583744793</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>577.7802149012412</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.0280010614580337</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.478439804368534</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.0046875351308759</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.812080951885037</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>34</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Utilities - Independent Power Producers</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1896825356288</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.4986</v>
+      </c>
+      <c r="G18" t="n">
+        <v>49.804</v>
+      </c>
+      <c r="H18" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="J18" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-15.26</v>
+      </c>
+      <c r="L18" t="n">
+        <v>43.58</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>97.78534923339012</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>97</v>
+      </c>
+      <c r="S18" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="V18" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>92.09</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.029875973669953</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>15265.02258</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.03377524162337</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>ADANIENSOL.NS</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.4588590165737962</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>40.07446</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.3217419306718889</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>36.82498128960079</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>722.2803075356056</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.0350039941826131</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.402766164711362</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.4395645603693158</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.057074426008933</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Utilities - Renewable</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>251640758272</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.5448</v>
+      </c>
+      <c r="G19" t="n">
+        <v>47.11999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>150.14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="J19" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="L19" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="R19" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="S19" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="T19" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="U19" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="W19" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.028412832815881</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>13806.46152</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.0305480434999632</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>ACMESOLAR.NS</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.4711379433871931</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>38.47247999999999</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.3088802692022707</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>36.04329204038034</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>688.5236753195049</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.0333680407371307</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.283751279898446</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.4724759199190803</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.72478856334317</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Telecom Services</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1619728400384</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.3462</v>
+      </c>
+      <c r="G20" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="J20" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-55.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>131.15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>98.63713798977854</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="R20" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="S20" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="U20" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="W20" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>84.84</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.0275239179732741</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12236.30352</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.0270739270642398</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>IDEA.NS</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.5329378008108371</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>53.55762000000001</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.429992869797656</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>31.48923893046965</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>472.6891413228398</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.0229080147699214</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.226898750001838</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.0212037872769425</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.302142479169568</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>79</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Household &amp; Personal Products</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>72107843584</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="G21" t="n">
+        <v>44.14400000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>106.48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="J21" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-22.03</v>
+      </c>
+      <c r="L21" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>77.00170357751279</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="S21" t="n">
+        <v>91.01000000000001</v>
+      </c>
+      <c r="T21" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>92.17</v>
+      </c>
+      <c r="V21" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="X21" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.0279067353142508</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13318.99272</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.0294694747381046</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>BAJAJCON.NS</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.4194459219385406</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>36.24268000000001</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.2909780901832104</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>31.54580671352748</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>676.8745279715645</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.0328034861151294</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.188886250155078</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-0.5376273026805292</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.834420810817372</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>56</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>195722395648</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.1158</v>
+      </c>
+      <c r="G22" t="n">
+        <v>36.608</v>
+      </c>
+      <c r="H22" t="n">
+        <v>146.84</v>
+      </c>
+      <c r="I22" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="J22" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-19.63</v>
+      </c>
+      <c r="L22" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>83.64565587734242</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>89.86</v>
+      </c>
+      <c r="R22" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="S22" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="T22" t="n">
+        <v>16.29333333333334</v>
+      </c>
+      <c r="U22" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="V22" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="W22" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="X22" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.0280786786962149</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12734.53425</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.0281763075685428</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>GRANULES.NS</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.3631152480446887</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>30.70578</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.2465245181091965</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>33.45263867771638</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>737.0142423454352</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.0357180473874277</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.09675050510793</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.7831622785146752</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>3.020392316251484</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>66</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Textile Manufacturing</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>129406001152</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.0159</v>
+      </c>
+      <c r="G23" t="n">
+        <v>43.332</v>
+      </c>
+      <c r="H23" t="n">
+        <v>118.39</v>
+      </c>
+      <c r="I23" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="J23" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-26.27</v>
+      </c>
+      <c r="L23" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>77.68313458262351</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="R23" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="S23" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>18.80333333333333</v>
+      </c>
+      <c r="U23" t="n">
+        <v>91.13</v>
+      </c>
+      <c r="V23" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="W23" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="X23" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>83.84</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>62</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.0271994964978701</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11949.54752</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.0264394535063925</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>ARVIND.NS</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.410870056622734</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>37.10839</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.2979285321056208</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>31.30986927981584</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>609.6305880681871</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.0295446315449073</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1.096353709774723</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-0.4586397624675689</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.6683709170401</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>65</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>395993808896</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.0273</v>
+      </c>
+      <c r="G24" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="H24" t="n">
+        <v>129.45</v>
+      </c>
+      <c r="I24" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="J24" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-11.05</v>
+      </c>
+      <c r="L24" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>96.763202725724</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="R24" t="n">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="S24" t="n">
+        <v>92.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="U24" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="V24" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="W24" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="X24" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.0282895526552275</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13686.912</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.0302835293858965</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>ATHERENERG.NS</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.4692897361491945</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>35.32373</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.2836002054358942</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>33.38900003081538</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>640.3314991355458</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.031032495053286</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1.09618347648861</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>-0.5371192493180633</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.335835182511038</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>72</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Household &amp; Personal Products</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>135433666560</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="G25" t="n">
+        <v>38.636</v>
+      </c>
+      <c r="H25" t="n">
+        <v>135.27</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="J25" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-22.01</v>
+      </c>
+      <c r="L25" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>92.16354344122658</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>90.78</v>
+      </c>
+      <c r="R25" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="S25" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="T25" t="n">
+        <v>16.92666666666667</v>
+      </c>
+      <c r="U25" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="V25" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="W25" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="X25" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>47</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.0276407097044196</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13066.272</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.0289103073122788</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>HONASA.NS</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.4366332708113268</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>32.63121</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.2619830312263683</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>32.37541745468396</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>667.3306332124721</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.0323409587097145</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1.055324615258023</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>-0.6468451885259124</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.416958774802203</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>98</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ACCENTMIC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6382436864</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.7461</v>
+      </c>
+      <c r="G26" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="H26" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="I26" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="J26" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>33.90119250425894</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="R26" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="S26" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="T26" t="n">
+        <v>19.22666666666667</v>
+      </c>
+      <c r="U26" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="V26" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="X26" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.0267712601503369</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12257.19072</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.0271201418813577</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>ACCENTMIC.NS</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.4692332049088986</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>29.98261</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.2407184732615806</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>30.13132777098924</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>577.9257458805648</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.0280081143507964</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.8397563694153317</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>-0.6343671077756139</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.789635432084074</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>38</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AIMTRON</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>11131658240</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.4114</v>
+      </c>
+      <c r="G27" t="n">
+        <v>58.044</v>
+      </c>
+      <c r="H27" t="n">
+        <v>147.15</v>
+      </c>
+      <c r="I27" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="J27" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-19.39</v>
+      </c>
+      <c r="L27" t="n">
+        <v>60.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>44.12265758091993</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="R27" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="S27" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="T27" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="U27" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="V27" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="W27" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="X27" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>84.01000000000001</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.0272546481486888</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>10586.52015</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.0234236323033939</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>AIMTRON.NS</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.5780602257632985</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>47.87674000000001</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.3843833394604956</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>34.15943750091908</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>354.5592930821004</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.0171830677133966</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0.8226692653166836</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>-0.0817102016201692</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.42315493896919</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>103</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AFIL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Credit Services</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6146965504</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6969</v>
+      </c>
+      <c r="G28" t="n">
+        <v>38.988</v>
+      </c>
+      <c r="H28" t="n">
+        <v>101.36</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="J28" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>12</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>91.23999999999999</v>
+      </c>
+      <c r="R28" t="n">
+        <v>90.78</v>
+      </c>
+      <c r="S28" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>20.40666666666666</v>
+      </c>
+      <c r="U28" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="V28" t="n">
+        <v>66.81999999999999</v>
+      </c>
+      <c r="W28" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="X28" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.0263105816552632</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11838.978</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.0261948084536513</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>AFIL.NS</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.547377089926515</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>31.09589</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.2496565564342148</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>29.79382848346513</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>489.8715369822738</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.0237407281520131</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.7382390711349027</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>-0.5112832742883765</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.348684635730755</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>112</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>303780003840</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6598000000000001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>37.064</v>
+      </c>
+      <c r="H29" t="n">
+        <v>120.27</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-6.23</v>
+      </c>
+      <c r="L29" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12</v>
+      </c>
+      <c r="O29" t="n">
+        <v>7</v>
+      </c>
+      <c r="P29" t="n">
+        <v>94.03747870528107</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="R29" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="S29" t="n">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="T29" t="n">
+        <v>19.13666666666667</v>
+      </c>
+      <c r="U29" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="V29" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="W29" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="X29" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>85.63</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>43</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.0277802109388433</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>12465.24473</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.0275804801757581</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>ANGELONE.NS</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.4765159887331489</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>28.17958</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.2262426611543349</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>31.57039639917315</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>530.0203501352431</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.0256864669564399</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0.7238338505163547</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>-0.6280966476359007</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.519012724926015</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>81</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas Equipment &amp; Services</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>18563803136</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8705000000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="H30" t="n">
+        <v>76.41</v>
+      </c>
+      <c r="I30" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="J30" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-18.31</v>
+      </c>
+      <c r="L30" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="M30" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>73.59454855195912</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>89.06</v>
+      </c>
+      <c r="R30" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="S30" t="n">
+        <v>90.78</v>
+      </c>
+      <c r="T30" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="U30" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="V30" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="W30" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="X30" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>82.14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.0277866993683513</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13204.6605</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.0292165043716608</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ASIANENE.NS</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.5540722189171483</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>29.50305</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.2368682763962202</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>29.93213024145944</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>486.1986632349407</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.0235627290428808</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.6951723730885645</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>-0.5449815206637248</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.254660221815805</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>105</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GOKULAGRO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>68710944768</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.6885</v>
+      </c>
+      <c r="G31" t="n">
+        <v>34</v>
+      </c>
+      <c r="H31" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J31" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>55.36626916524702</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="R31" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="S31" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="T31" t="n">
+        <v>18.99666666666666</v>
+      </c>
+      <c r="U31" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="V31" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="W31" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="X31" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>86.58</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.0280884113404771</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>12743.36388</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.0281958439226577</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>GOKULAGRO.NS</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.5008432168631864</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>25.52885</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.2049610022651098</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>31.71494415033976</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>506.5847847391847</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.024550705138997</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.6267512688876835</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>-0.6654017969597787</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.251392147852311</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>84</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JINDALSAW</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>159768723456</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="G32" t="n">
+        <v>38.348</v>
+      </c>
+      <c r="H32" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="L32" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="M32" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>78.87563884156728</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="R32" t="n">
+        <v>91.23999999999999</v>
+      </c>
+      <c r="S32" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="T32" t="n">
+        <v>20.32333333333333</v>
+      </c>
+      <c r="U32" t="n">
+        <v>92.63</v>
+      </c>
+      <c r="V32" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="X32" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.0284647402519457</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>11547.4614</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.0255498016381931</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>JINDALSAW.NS</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.4574179932599757</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>29.48897</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.2367552336656667</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>31.87605328504985</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>418.1215486239031</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.0202634961841802</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.5975496310704044</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>-0.4689589914288395</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.306353575668774</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>152</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ARROWGREEN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Packaging &amp; Containers</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>8101468672</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="G33" t="n">
+        <v>31.128</v>
+      </c>
+      <c r="H33" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J33" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="M33" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7</v>
+      </c>
+      <c r="P33" t="n">
+        <v>51.27768313458262</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="R33" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="S33" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="T33" t="n">
+        <v>17.49666666666667</v>
+      </c>
+      <c r="U33" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="V33" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="W33" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="X33" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>58</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.0272903345109832</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>12029.49648</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.0266163478036257</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>ARROWGREEN.NS</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.5641082651504327</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>23.22205</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.1864406208133344</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>29.517166093122</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>418.6028522060468</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.0202868216820703</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.4711015874421206</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>-0.5966347029974316</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.8351261921618723</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>143</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GANESHHOU</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Real Estate - Development</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>65104470016</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="G34" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="H34" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="I34" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="J34" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>60.45</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>42.4190800681431</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="R34" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="S34" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="T34" t="n">
+        <v>12.41333333333333</v>
+      </c>
+      <c r="U34" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="V34" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="W34" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="X34" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>76.64</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>137</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.0248636618749614</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>8810.5344</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.0194941033746583</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>GANESHHOU.NS</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.4280408466931638</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>22.9255</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.1840597385870798</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>25.67260896078806</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>359.8620434351843</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.0174400558114724</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.3998219995059104</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>-0.5180832687036515</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.9340744057366056</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>139</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EMKAY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>7947385856</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="G35" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="H35" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="I35" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="J35" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="K35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L35" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N35" t="n">
+        <v>12</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>47.52981260647359</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>86.87</v>
+      </c>
+      <c r="R35" t="n">
+        <v>69.93000000000001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="T35" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="V35" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="W35" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="X35" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>121</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.0251653738470871</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>9025.657349999999</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.0199700823374737</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>EMKAY.NS</t>
+        </is>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.5483131722101512</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>26.9656</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.216496097657358</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>26.4886744146486</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>289.8563349249213</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.0140473571765008</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.3787954146786499</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>-0.36054529019739</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.6908377071296576</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EMAMIREAL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Real Estate - Development</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4448897536</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6276</v>
+      </c>
+      <c r="G36" t="n">
+        <v>35.662</v>
+      </c>
+      <c r="H36" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-25.35</v>
+      </c>
+      <c r="L36" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="M36" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="R36" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="S36" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="T36" t="n">
+        <v>14.00666666666667</v>
+      </c>
+      <c r="U36" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="V36" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="X36" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>141</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.0248085102241428</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>8186.725259999999</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.018113869292465</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>EMAMIREAL.NS</t>
+        </is>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.5324664795983409</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>30.18156</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.2423157638328615</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>25.96236736457493</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>243.7934439005372</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.0118150034038314</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0.3565952341329416</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>-0.2652521948848409</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.6697045688245663</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>159</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BCG</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Advertising Agencies</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24403929088</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="G37" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="H37" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="I37" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="J37" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-13.47</v>
+      </c>
+      <c r="L37" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="N37" t="n">
+        <v>11</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="R37" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="S37" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>15.90666666666667</v>
+      </c>
+      <c r="U37" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="W37" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="X37" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>186</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.0236697908454748</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7984.742399999999</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.0176669639659562</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>BCG.NS</t>
+        </is>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.8497507003346279</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>27.57336</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.2213755614301736</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>24.26692633421452</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>171.3462053611135</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.008303980481120301</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.2289686432389032</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>-0.2080865768318734</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.2694539035375157</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>177</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HMVL</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Publishing</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5927500288</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G38" t="n">
+        <v>24.554</v>
+      </c>
+      <c r="H38" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="I38" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="J38" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="L38" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="N38" t="n">
+        <v>11</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>16.18398637137989</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>80.88</v>
+      </c>
+      <c r="R38" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="S38" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="T38" t="n">
+        <v>15.33666666666667</v>
+      </c>
+      <c r="U38" t="n">
+        <v>87.56</v>
+      </c>
+      <c r="V38" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="W38" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="X38" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>286</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.0209316735930651</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4162.8304</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.0092106383636355</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>HMVL.NS</t>
+        </is>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.3888302195570894</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>21.5714</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.1731882072346223</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>22.3100782310852</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>57.37742878240858</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.0027806921528366</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.0599834227056994</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>-0.0863700066611193</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.1542663601970691</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -586,16 +6609,804 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rebalance Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FINAL_WEIGHT_CURRENT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FINAL_WEIGHT_TARGET</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WEIGHT_CHANGE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ACTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CPPLUS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0432464205528206</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0433257368359144</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.931628309379435e-05</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0309951605301575</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.031032495053286</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.73345231285023e-05</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0398897363116996</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.039911293914623</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.155760292340408e-05</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0356993180804084</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0357180473874277</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.872930701929398e-05</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.032323328115075</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0323409587097145</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.763059463950195e-05</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACCENTMIC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0279926956258366</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0280081143507964</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.541872495980021e-05</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>APCOTEXIND</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0401848322138681</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0401992938730168</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.446165914870123e-05</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GOKULAGRO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0245384909316531</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.024550705138997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.221420734389897e-05</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0256743795513019</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0256864669564399</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.208740513800044e-05</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0256261037836203</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0256380338005201</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.193001689979781e-05</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0295328015069966</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0295446315449073</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.183003791070322e-05</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AFIL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0237301417651582</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0237407281520131</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.058638685489874e-05</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BLISSGVS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0194525975089617</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0194630528749825</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.045536602079997e-05</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IOLCP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.037178024470947</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0371882733022332</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.024883128619702e-05</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AIMTRON</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0171736129296519</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0171830677133966</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.454783744700102e-06</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ARROWGREEN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.0202776266984467</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0202868216820703</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.194983623599801e-06</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GANESHHOU</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0174313011124545</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0174400558114724</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8.754699017898826e-06</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EFFWA</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0279928169374511</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0280010614580337</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8.244520582598863e-06</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0339968623427598</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0340033629881677</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.500645407900296e-06</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMAMIREAL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0118087817746954</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0118150034038314</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6.221629135999204e-06</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0325591148101234</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0325651061035051</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.991293381697738e-06</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.022903325756553</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0229080147699214</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.689013368398831e-06</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IBULLSLTD</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0343564537743648</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0343593666507723</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.912876407502873e-06</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BCG</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.0083018007119267</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.008303980481120301</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.179769193600897e-06</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CONFIPET</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.0395089093047837</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0395096397302414</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.304254577011893e-07</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0350044954217299</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0350039941826131</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-5.012391167957819e-07</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0235695638874149</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0235627290428808</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-6.834844534099604e-06</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IDEAFORGE</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0329216721978759</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0329134749965033</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-8.197201372600604e-06</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HMVL</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0027980149326662</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0027806921528366</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.732277982959994e-05</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.0333872810327153</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0333680407371307</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-1.924029558460216e-05</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EMKAY</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0140716535506918</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0140473571765008</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-2.429637419099941e-05</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0328295136584142</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0328034861151294</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-2.602754328480394e-05</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0414219077739328</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0413772095426265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-4.469823130630324e-05</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>JINDALSAW</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0203137942893421</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0202634961841802</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-5.029810516189726e-05</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0295648868062069</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0294898582135803</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-7.502859262659839e-05</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0317425793472927</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0316663489686118</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-7.623037868090266e-05</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -610,10 +7421,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -623,6 +7441,1201 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Current_Price</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMA50</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ATR_Stop</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hard_Stop</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Stop_Type</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>169.11</v>
+      </c>
+      <c r="C4" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>137.62</v>
+      </c>
+      <c r="F4" t="n">
+        <v>143.74</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>494.65</v>
+      </c>
+      <c r="C5" t="n">
+        <v>440.27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="E5" t="n">
+        <v>438.43</v>
+      </c>
+      <c r="F5" t="n">
+        <v>420.45</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>564.05</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500.36</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="E6" t="n">
+        <v>487.18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>479.44</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1048.45</v>
+      </c>
+      <c r="C7" t="n">
+        <v>910.22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="E7" t="n">
+        <v>915.74</v>
+      </c>
+      <c r="F7" t="n">
+        <v>891.1799999999999</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>413</v>
+      </c>
+      <c r="C8" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>367.78</v>
+      </c>
+      <c r="F8" t="n">
+        <v>351.05</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JINDALSAW</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>226.95</v>
+      </c>
+      <c r="C9" t="n">
+        <v>225.67</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="E9" t="n">
+        <v>195.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>192.91</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>335</v>
+      </c>
+      <c r="C10" t="n">
+        <v>310.76</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>298.96</v>
+      </c>
+      <c r="F10" t="n">
+        <v>284.75</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>766.65</v>
+      </c>
+      <c r="C11" t="n">
+        <v>720.04</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="E11" t="n">
+        <v>701.99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>651.65</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ACCENTMIC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>475.85</v>
+      </c>
+      <c r="C12" t="n">
+        <v>430.48</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="E12" t="n">
+        <v>422.65</v>
+      </c>
+      <c r="F12" t="n">
+        <v>404.47</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AFIL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>328.69</v>
+      </c>
+      <c r="D14" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>303.15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>315.18</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMAMIREAL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E15" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="F15" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GANESHHOU</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>766.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>692.97</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="E16" t="n">
+        <v>671.1799999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>651.35</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ARROWGREEN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>589.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>515.37</v>
+      </c>
+      <c r="D17" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="E17" t="n">
+        <v>488.48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>501.16</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMKAY</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>269.21</v>
+      </c>
+      <c r="C18" t="n">
+        <v>237.72</v>
+      </c>
+      <c r="D18" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="E18" t="n">
+        <v>213.34</v>
+      </c>
+      <c r="F18" t="n">
+        <v>228.83</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GOKULAGRO</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>232.21</v>
+      </c>
+      <c r="C19" t="n">
+        <v>220.98</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>197.38</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AIMTRON</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1212.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1077.07</v>
+      </c>
+      <c r="D20" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1030.67</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1030.37</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>340.35</v>
+      </c>
+      <c r="C22" t="n">
+        <v>298.05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="E22" t="n">
+        <v>298.85</v>
+      </c>
+      <c r="F22" t="n">
+        <v>289.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONFIPET</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="F23" t="n">
+        <v>62.31</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CPPLUS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3487.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2567.79</v>
+      </c>
+      <c r="D24" t="n">
+        <v>162.05</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3001.55</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2964.54</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IDEAFORGE</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>928</v>
+      </c>
+      <c r="C25" t="n">
+        <v>720.83</v>
+      </c>
+      <c r="D25" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="E25" t="n">
+        <v>762.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>788.8</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IBULLSLTD</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="C26" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E26" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1228.4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>883.67</v>
+      </c>
+      <c r="D27" t="n">
+        <v>58</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1054.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1044.14</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BLISSGVS</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>320.69</v>
+      </c>
+      <c r="D28" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="E28" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="F28" t="n">
+        <v>359.89</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IOLCP</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="C29" t="n">
+        <v>108.74</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="E29" t="n">
+        <v>106.49</v>
+      </c>
+      <c r="F29" t="n">
+        <v>110.71</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>415.7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>352.93</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>339.97</v>
+      </c>
+      <c r="F30" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1311.17</v>
+      </c>
+      <c r="D31" t="n">
+        <v>95.70999999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1255.98</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1311.63</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1505.7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="D32" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1342.29</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1279.84</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>693.6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>579.78</v>
+      </c>
+      <c r="D33" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>594.29</v>
+      </c>
+      <c r="F33" t="n">
+        <v>589.5599999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>APCOTEXIND</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>543.25</v>
+      </c>
+      <c r="C34" t="n">
+        <v>458.84</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="E34" t="n">
+        <v>474.75</v>
+      </c>
+      <c r="F34" t="n">
+        <v>461.76</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2970</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2600.62</v>
+      </c>
+      <c r="D35" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2698.53</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2524.5</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EFFWA</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>257.57</v>
+      </c>
+      <c r="D36" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="E36" t="n">
+        <v>255.3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>268.85</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1556.1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1352.05</v>
+      </c>
+      <c r="D37" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1371.07</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1322.68</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BCG</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HMVL</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E39" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="F39" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
